--- a/lexicon.xlsx
+++ b/lexicon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjohns/Desktop/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9928F9C8-9270-BD4D-AC85-CE4B169B5DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3661E82F-008E-4042-9A82-F31703B8EE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="660" windowWidth="30620" windowHeight="20540" xr2:uid="{2088926B-C3F6-4744-A3EE-0710A9EB89B3}"/>
+    <workbookView xWindow="14260" yWindow="660" windowWidth="18720" windowHeight="20540" xr2:uid="{2088926B-C3F6-4744-A3EE-0710A9EB89B3}"/>
   </bookViews>
   <sheets>
     <sheet name="lexicon" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1219">
   <si>
     <t>oodham</t>
   </si>
@@ -3555,6 +3555,141 @@
   </si>
   <si>
     <t>Tohono O'odham || Any</t>
+  </si>
+  <si>
+    <t>lai</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>lalai</t>
+  </si>
+  <si>
+    <t>kings</t>
+  </si>
+  <si>
+    <t>kovnal</t>
+  </si>
+  <si>
+    <t>council member</t>
+  </si>
+  <si>
+    <t>kokovnal</t>
+  </si>
+  <si>
+    <t>council members</t>
+  </si>
+  <si>
+    <t>pikcul</t>
+  </si>
+  <si>
+    <t>picture</t>
+  </si>
+  <si>
+    <t>pipikcul</t>
+  </si>
+  <si>
+    <t>nouns</t>
+  </si>
+  <si>
+    <t>vepgi-kahon</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>vepgi-kakhon</t>
+  </si>
+  <si>
+    <t>TVs</t>
+  </si>
+  <si>
+    <t>[ɽɑi]</t>
+  </si>
+  <si>
+    <t>[ˈɽɑ.ɽɑi]</t>
+  </si>
+  <si>
+    <t>[ˈkɔ.kɔv.nɑɽ]</t>
+  </si>
+  <si>
+    <t>[ˈkɔv.nɑɽ]</t>
+  </si>
+  <si>
+    <t>[ˈpik.cuɽ]</t>
+  </si>
+  <si>
+    <t>[ˈvɯp.gi ˈkɑ.hɔn]</t>
+  </si>
+  <si>
+    <t>[ˈvɯp.gi ˈkɑk.hɔn]</t>
+  </si>
+  <si>
+    <t>[ˈpi.pik.cuɽ]</t>
+  </si>
+  <si>
+    <t>pasahi:lo</t>
+  </si>
+  <si>
+    <t>train (that people ride on)</t>
+  </si>
+  <si>
+    <t>vainom kalit</t>
+  </si>
+  <si>
+    <t>train (for cargo)</t>
+  </si>
+  <si>
+    <t>papsahi:lo</t>
+  </si>
+  <si>
+    <t>vapainom kaklit</t>
+  </si>
+  <si>
+    <t>0 - 1</t>
+  </si>
+  <si>
+    <t>2 - 1</t>
+  </si>
+  <si>
+    <t>[ˈpɑ.sɑ.hiː.ɽɔ]</t>
+  </si>
+  <si>
+    <t>[ˈvɑi.nom ˈkɑ.ɽit̪]</t>
+  </si>
+  <si>
+    <t>[ˈpɑp.sɑ.hiː.ɽɔ]</t>
+  </si>
+  <si>
+    <t>[ˈvɑ.pɑi.nom ˈkɑk.ɽit̪]</t>
+  </si>
+  <si>
+    <t>trains (that people ride on)</t>
+  </si>
+  <si>
+    <t>trains (for cargo)</t>
+  </si>
+  <si>
+    <t>vainom ki:</t>
+  </si>
+  <si>
+    <t>trailer home</t>
+  </si>
+  <si>
+    <t>2 - 8</t>
+  </si>
+  <si>
+    <t>[ˈvɑi.nom ˈkiː]</t>
+  </si>
+  <si>
+    <t>vapainom ki:kĭ</t>
+  </si>
+  <si>
+    <t>[ˈvɑ.pɑi.nom ˈkiː.kĭ]</t>
+  </si>
+  <si>
+    <t>trailer homes</t>
   </si>
 </sst>
 </file>
@@ -4045,7 +4180,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4054,6 +4189,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -4430,13 +4571,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD9D216-8ECF-2E4A-B0B5-5034F16CC910}">
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.5" bestFit="1" customWidth="1"/>
@@ -4458,7 +4599,7 @@
       <c r="C1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>653</v>
       </c>
       <c r="E1" t="s">
@@ -4502,7 +4643,7 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="6">
         <v>7</v>
       </c>
       <c r="E2" t="s">
@@ -4543,7 +4684,7 @@
       <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>7</v>
       </c>
       <c r="E3" t="s">
@@ -4587,7 +4728,7 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>7</v>
       </c>
       <c r="E4" t="s">
@@ -4628,7 +4769,7 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>2</v>
       </c>
       <c r="E5" t="s">
@@ -4669,7 +4810,7 @@
       <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
@@ -4710,7 +4851,7 @@
       <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>7</v>
       </c>
       <c r="E7" t="s">
@@ -4751,7 +4892,7 @@
       <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="6">
         <v>7</v>
       </c>
       <c r="E8" t="s">
@@ -4792,7 +4933,7 @@
       <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>4</v>
       </c>
       <c r="E9" t="s">
@@ -4833,7 +4974,7 @@
       <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="6">
         <v>3</v>
       </c>
       <c r="E10" t="s">
@@ -4874,7 +5015,7 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>2</v>
       </c>
       <c r="E11" t="s">
@@ -4915,7 +5056,7 @@
       <c r="C12" t="s">
         <v>12</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>2</v>
       </c>
       <c r="E12" t="s">
@@ -4956,7 +5097,7 @@
       <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="6">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -4997,7 +5138,7 @@
       <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="6">
         <v>7</v>
       </c>
       <c r="E14" t="s">
@@ -5038,7 +5179,7 @@
       <c r="C15" t="s">
         <v>12</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="6">
         <v>7</v>
       </c>
       <c r="E15" t="s">
@@ -5079,7 +5220,7 @@
       <c r="C16" t="s">
         <v>12</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="6">
         <v>7</v>
       </c>
       <c r="E16" t="s">
@@ -5120,7 +5261,7 @@
       <c r="C17" t="s">
         <v>12</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="6">
         <v>2</v>
       </c>
       <c r="E17" t="s">
@@ -5187,7 +5328,7 @@
       <c r="C19" t="s">
         <v>12</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="6">
         <v>1</v>
       </c>
       <c r="E19" t="s">
@@ -5257,7 +5398,7 @@
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>2</v>
       </c>
       <c r="E21" t="s">
@@ -5298,7 +5439,7 @@
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="6">
         <v>2</v>
       </c>
       <c r="E22" t="s">
@@ -5339,7 +5480,7 @@
       <c r="C23" t="s">
         <v>12</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="6">
         <v>1</v>
       </c>
       <c r="E23" t="s">
@@ -5380,7 +5521,7 @@
       <c r="C24" t="s">
         <v>12</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="6">
         <v>7</v>
       </c>
       <c r="E24" t="s">
@@ -5421,7 +5562,7 @@
       <c r="C25" t="s">
         <v>12</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="6">
         <v>2</v>
       </c>
       <c r="E25" t="s">
@@ -5491,7 +5632,7 @@
       <c r="C27" t="s">
         <v>12</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="6">
         <v>2</v>
       </c>
       <c r="E27" t="s">
@@ -5532,7 +5673,7 @@
       <c r="C28" t="s">
         <v>12</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="6">
         <v>7</v>
       </c>
       <c r="E28" t="s">
@@ -5573,7 +5714,7 @@
       <c r="C29" t="s">
         <v>12</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="6">
         <v>7</v>
       </c>
       <c r="E29" t="s">
@@ -5614,7 +5755,7 @@
       <c r="C30" t="s">
         <v>12</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="6">
         <v>2</v>
       </c>
       <c r="E30" t="s">
@@ -5655,7 +5796,7 @@
       <c r="C31" t="s">
         <v>12</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="6">
         <v>1</v>
       </c>
       <c r="E31" t="s">
@@ -5696,7 +5837,7 @@
       <c r="C32" t="s">
         <v>12</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="6">
         <v>1</v>
       </c>
       <c r="E32" t="s">
@@ -5737,7 +5878,7 @@
       <c r="C33" t="s">
         <v>12</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="6">
         <v>1</v>
       </c>
       <c r="E33" t="s">
@@ -5778,7 +5919,7 @@
       <c r="C34" t="s">
         <v>12</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="6">
         <v>1</v>
       </c>
       <c r="E34" t="s">
@@ -5819,7 +5960,7 @@
       <c r="C35" t="s">
         <v>12</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="6">
         <v>2</v>
       </c>
       <c r="E35" t="s">
@@ -5860,7 +6001,7 @@
       <c r="C36" t="s">
         <v>12</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="6">
         <v>4</v>
       </c>
       <c r="E36" t="s">
@@ -5901,7 +6042,7 @@
       <c r="C37" t="s">
         <v>12</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="6">
         <v>2</v>
       </c>
       <c r="E37" t="s">
@@ -5942,7 +6083,7 @@
       <c r="C38" t="s">
         <v>12</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="6">
         <v>7</v>
       </c>
       <c r="E38" t="s">
@@ -5983,7 +6124,7 @@
       <c r="C39" t="s">
         <v>12</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="6">
         <v>7</v>
       </c>
       <c r="E39" t="s">
@@ -6024,7 +6165,7 @@
       <c r="C40" t="s">
         <v>12</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="6">
         <v>3</v>
       </c>
       <c r="E40" t="s">
@@ -6065,7 +6206,7 @@
       <c r="C41" t="s">
         <v>12</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="6">
         <v>3</v>
       </c>
       <c r="E41" t="s">
@@ -6106,7 +6247,7 @@
       <c r="C42" t="s">
         <v>12</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="6">
         <v>2</v>
       </c>
       <c r="E42" t="s">
@@ -6147,7 +6288,7 @@
       <c r="C43" t="s">
         <v>12</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="6">
         <v>2</v>
       </c>
       <c r="E43" t="s">
@@ -6188,7 +6329,7 @@
       <c r="C44" t="s">
         <v>12</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="6">
         <v>1</v>
       </c>
       <c r="E44" t="s">
@@ -6229,7 +6370,7 @@
       <c r="C45" t="s">
         <v>12</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="6">
         <v>2</v>
       </c>
       <c r="E45" t="s">
@@ -6270,7 +6411,7 @@
       <c r="C46" t="s">
         <v>12</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="6">
         <v>1</v>
       </c>
       <c r="E46" t="s">
@@ -6311,7 +6452,7 @@
       <c r="C47" t="s">
         <v>12</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="6">
         <v>1</v>
       </c>
       <c r="E47" t="s">
@@ -6352,7 +6493,7 @@
       <c r="C48" t="s">
         <v>12</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="6">
         <v>2</v>
       </c>
       <c r="E48" t="s">
@@ -6393,7 +6534,7 @@
       <c r="C49" t="s">
         <v>12</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="6">
         <v>7</v>
       </c>
       <c r="E49" t="s">
@@ -6434,7 +6575,7 @@
       <c r="C50" t="s">
         <v>12</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="6">
         <v>4</v>
       </c>
       <c r="E50" t="s">
@@ -6475,7 +6616,7 @@
       <c r="C51" t="s">
         <v>12</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="6">
         <v>2</v>
       </c>
       <c r="E51" t="s">
@@ -6516,7 +6657,7 @@
       <c r="C52" t="s">
         <v>12</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="6">
         <v>2</v>
       </c>
       <c r="E52" t="s">
@@ -6557,7 +6698,7 @@
       <c r="C53" t="s">
         <v>12</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="6">
         <v>4</v>
       </c>
       <c r="E53" t="s">
@@ -6598,7 +6739,7 @@
       <c r="C54" t="s">
         <v>12</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="6">
         <v>1</v>
       </c>
       <c r="E54" t="s">
@@ -6639,7 +6780,7 @@
       <c r="C55" t="s">
         <v>12</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="6">
         <v>1</v>
       </c>
       <c r="E55" t="s">
@@ -6680,7 +6821,7 @@
       <c r="C56" t="s">
         <v>12</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="6">
         <v>4</v>
       </c>
       <c r="E56" t="s">
@@ -6721,7 +6862,7 @@
       <c r="C57" t="s">
         <v>12</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="6">
         <v>1</v>
       </c>
       <c r="E57" t="s">
@@ -6762,7 +6903,7 @@
       <c r="C58" t="s">
         <v>12</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="6">
         <v>1</v>
       </c>
       <c r="E58" t="s">
@@ -6803,7 +6944,7 @@
       <c r="C59" t="s">
         <v>12</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="6">
         <v>1</v>
       </c>
       <c r="E59" t="s">
@@ -6844,7 +6985,7 @@
       <c r="C60" t="s">
         <v>12</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="6">
         <v>3</v>
       </c>
       <c r="E60" t="s">
@@ -6885,7 +7026,7 @@
       <c r="C61" t="s">
         <v>12</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="6">
         <v>1</v>
       </c>
       <c r="E61" t="s">
@@ -6926,7 +7067,7 @@
       <c r="C62" t="s">
         <v>12</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="6">
         <v>2</v>
       </c>
       <c r="E62" t="s">
@@ -6967,7 +7108,7 @@
       <c r="C63" t="s">
         <v>12</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="6">
         <v>2</v>
       </c>
       <c r="E63" t="s">
@@ -7008,7 +7149,7 @@
       <c r="C64" t="s">
         <v>12</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="6">
         <v>1</v>
       </c>
       <c r="E64" t="s">
@@ -7049,7 +7190,7 @@
       <c r="C65" t="s">
         <v>12</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="6">
         <v>2</v>
       </c>
       <c r="E65" t="s">
@@ -7090,7 +7231,7 @@
       <c r="C66" t="s">
         <v>12</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="6">
         <v>4</v>
       </c>
       <c r="E66" t="s">
@@ -7157,7 +7298,7 @@
       <c r="C68" t="s">
         <v>12</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="6">
         <v>2</v>
       </c>
       <c r="E68" t="s">
@@ -7198,7 +7339,7 @@
       <c r="C69" t="s">
         <v>12</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="6">
         <v>4</v>
       </c>
       <c r="E69" t="s">
@@ -7239,7 +7380,7 @@
       <c r="C70" t="s">
         <v>12</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="6">
         <v>2</v>
       </c>
       <c r="E70" t="s">
@@ -7280,7 +7421,7 @@
       <c r="C71" t="s">
         <v>12</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="6">
         <v>4</v>
       </c>
       <c r="E71" t="s">
@@ -7377,7 +7518,7 @@
       <c r="C74" t="s">
         <v>12</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="6">
         <v>1</v>
       </c>
       <c r="E74" t="s">
@@ -7418,7 +7559,7 @@
       <c r="C75" t="s">
         <v>12</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="6">
         <v>2</v>
       </c>
       <c r="E75" t="s">
@@ -7459,7 +7600,7 @@
       <c r="C76" t="s">
         <v>12</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="6">
         <v>2</v>
       </c>
       <c r="E76" t="s">
@@ -7500,7 +7641,7 @@
       <c r="C77" t="s">
         <v>12</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="6">
         <v>2</v>
       </c>
       <c r="E77" t="s">
@@ -7541,7 +7682,7 @@
       <c r="C78" t="s">
         <v>12</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="6">
         <v>1</v>
       </c>
       <c r="E78" t="s">
@@ -7582,7 +7723,7 @@
       <c r="C79" t="s">
         <v>12</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="6">
         <v>3</v>
       </c>
       <c r="E79" t="s">
@@ -7623,7 +7764,7 @@
       <c r="C80" t="s">
         <v>12</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="6">
         <v>4</v>
       </c>
       <c r="E80" t="s">
@@ -7713,7 +7854,7 @@
       <c r="C83" t="s">
         <v>12</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="6">
         <v>4</v>
       </c>
       <c r="E83" t="s">
@@ -7754,7 +7895,7 @@
       <c r="C84" t="s">
         <v>12</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="6">
         <v>1</v>
       </c>
       <c r="E84" t="s">
@@ -7795,7 +7936,7 @@
       <c r="C85" t="s">
         <v>12</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="6">
         <v>3</v>
       </c>
       <c r="E85" t="s">
@@ -7836,7 +7977,7 @@
       <c r="C86" t="s">
         <v>12</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="6">
         <v>2</v>
       </c>
       <c r="E86" t="s">
@@ -7877,7 +8018,7 @@
       <c r="C87" t="s">
         <v>12</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="6">
         <v>2</v>
       </c>
       <c r="E87" t="s">
@@ -7944,7 +8085,7 @@
       <c r="C89" t="s">
         <v>12</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="6">
         <v>1</v>
       </c>
       <c r="E89" t="s">
@@ -7985,7 +8126,7 @@
       <c r="C90" t="s">
         <v>12</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="6">
         <v>7</v>
       </c>
       <c r="E90" t="s">
@@ -8026,7 +8167,7 @@
       <c r="C91" t="s">
         <v>12</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="6">
         <v>2</v>
       </c>
       <c r="E91" t="s">
@@ -8067,7 +8208,7 @@
       <c r="C92" t="s">
         <v>12</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="6">
         <v>2</v>
       </c>
       <c r="E92" t="s">
@@ -8111,7 +8252,7 @@
       <c r="C93" t="s">
         <v>12</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="6">
         <v>7</v>
       </c>
       <c r="E93" t="s">
@@ -8152,7 +8293,7 @@
       <c r="C94" t="s">
         <v>12</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="6">
         <v>2</v>
       </c>
       <c r="E94" t="s">
@@ -8193,7 +8334,7 @@
       <c r="C95" t="s">
         <v>12</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="6">
         <v>2</v>
       </c>
       <c r="E95" t="s">
@@ -8234,7 +8375,7 @@
       <c r="C96" t="s">
         <v>12</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="6">
         <v>7</v>
       </c>
       <c r="E96" t="s">
@@ -8275,7 +8416,7 @@
       <c r="C97" t="s">
         <v>12</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="6">
         <v>1</v>
       </c>
       <c r="E97" t="s">
@@ -8356,7 +8497,7 @@
       <c r="C100" t="s">
         <v>12</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="6">
         <v>1</v>
       </c>
       <c r="E100" t="s">
@@ -8411,7 +8552,7 @@
       <c r="C102" t="s">
         <v>12</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="6">
         <v>2</v>
       </c>
       <c r="E102" t="s">
@@ -8446,7 +8587,7 @@
       <c r="C103" t="s">
         <v>12</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="6">
         <v>4</v>
       </c>
       <c r="E103" t="s">
@@ -8481,7 +8622,7 @@
       <c r="C104" t="s">
         <v>12</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="6">
         <v>1</v>
       </c>
       <c r="E104" t="s">
@@ -8533,7 +8674,7 @@
       <c r="C106" t="s">
         <v>12</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="6">
         <v>1</v>
       </c>
       <c r="E106" t="s">
@@ -8562,7 +8703,7 @@
       <c r="C107" t="s">
         <v>12</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="6">
         <v>4</v>
       </c>
       <c r="E107" t="s">
@@ -8597,7 +8738,7 @@
       <c r="C108" t="s">
         <v>12</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="6">
         <v>7</v>
       </c>
       <c r="E108" t="s">
@@ -8626,7 +8767,7 @@
       <c r="C109" t="s">
         <v>12</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="6">
         <v>4</v>
       </c>
       <c r="E109" t="s">
@@ -8655,7 +8796,7 @@
       <c r="C110" t="s">
         <v>12</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="6">
         <v>7</v>
       </c>
       <c r="E110" t="s">
@@ -8684,7 +8825,7 @@
       <c r="C111" t="s">
         <v>12</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="6">
         <v>7</v>
       </c>
       <c r="E111" t="s">
@@ -8713,7 +8854,7 @@
       <c r="C112" t="s">
         <v>12</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="6">
         <v>7</v>
       </c>
       <c r="E112" t="s">
@@ -8742,7 +8883,7 @@
       <c r="C113" t="s">
         <v>12</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="6">
         <v>7</v>
       </c>
       <c r="E113" t="s">
@@ -8771,7 +8912,7 @@
       <c r="C114" t="s">
         <v>12</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="6">
         <v>7</v>
       </c>
       <c r="E114" t="s">
@@ -8800,7 +8941,7 @@
       <c r="C115" t="s">
         <v>12</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="6">
         <v>2</v>
       </c>
       <c r="E115" t="s">
@@ -8829,7 +8970,7 @@
       <c r="C116" t="s">
         <v>12</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="6">
         <v>7</v>
       </c>
       <c r="E116" t="s">
@@ -8858,7 +8999,7 @@
       <c r="C117" t="s">
         <v>12</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="6">
         <v>7</v>
       </c>
       <c r="E117" t="s">
@@ -8887,7 +9028,7 @@
       <c r="C118" t="s">
         <v>12</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="6">
         <v>7</v>
       </c>
       <c r="E118" t="s">
@@ -8916,7 +9057,7 @@
       <c r="C119" t="s">
         <v>12</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="6">
         <v>7</v>
       </c>
       <c r="E119" t="s">
@@ -8945,7 +9086,7 @@
       <c r="C120" t="s">
         <v>12</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="6">
         <v>1</v>
       </c>
       <c r="E120" t="s">
@@ -8974,7 +9115,7 @@
       <c r="C121" t="s">
         <v>12</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="6">
         <v>7</v>
       </c>
       <c r="E121" t="s">
@@ -9003,7 +9144,7 @@
       <c r="C122" t="s">
         <v>12</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="6">
         <v>7</v>
       </c>
       <c r="E122" t="s">
@@ -9032,7 +9173,7 @@
       <c r="C123" t="s">
         <v>12</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="6">
         <v>2</v>
       </c>
       <c r="E123" t="s">
@@ -9061,7 +9202,7 @@
       <c r="C124" t="s">
         <v>12</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="6">
         <v>1</v>
       </c>
       <c r="E124" t="s">
@@ -9090,7 +9231,7 @@
       <c r="C125" t="s">
         <v>12</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="6">
         <v>7</v>
       </c>
       <c r="E125" t="s">
@@ -9119,7 +9260,7 @@
       <c r="C126" t="s">
         <v>12</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="6">
         <v>1</v>
       </c>
       <c r="E126" t="s">
@@ -9148,7 +9289,7 @@
       <c r="C127" t="s">
         <v>12</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="6">
         <v>7</v>
       </c>
       <c r="E127" s="2" t="s">
@@ -9177,7 +9318,7 @@
       <c r="C128" t="s">
         <v>12</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="6">
         <v>2</v>
       </c>
       <c r="E128" s="2" t="s">
@@ -9206,7 +9347,7 @@
       <c r="C129" t="s">
         <v>12</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="6">
         <v>1</v>
       </c>
       <c r="E129" s="2" t="s">
@@ -9235,7 +9376,7 @@
       <c r="C130" t="s">
         <v>12</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="6">
         <v>2</v>
       </c>
       <c r="E130" s="2" t="s">
@@ -9264,7 +9405,7 @@
       <c r="C131" t="s">
         <v>12</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="6">
         <v>3</v>
       </c>
       <c r="E131" s="2" t="s">
@@ -9293,7 +9434,7 @@
       <c r="C132" t="s">
         <v>12</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="6">
         <v>4</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -9322,7 +9463,7 @@
       <c r="C133" t="s">
         <v>12</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="6">
         <v>1</v>
       </c>
       <c r="E133" s="2" t="s">
@@ -9351,7 +9492,7 @@
       <c r="C134" t="s">
         <v>12</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="6">
         <v>1</v>
       </c>
       <c r="E134" s="2" t="s">
@@ -9380,7 +9521,7 @@
       <c r="C135" t="s">
         <v>12</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="6">
         <v>1</v>
       </c>
       <c r="E135" s="2" t="s">
@@ -9409,7 +9550,7 @@
       <c r="C136" t="s">
         <v>12</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="6">
         <v>1</v>
       </c>
       <c r="E136" s="2" t="s">
@@ -9438,7 +9579,7 @@
       <c r="C137" t="s">
         <v>12</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="6">
         <v>1</v>
       </c>
       <c r="E137" s="2" t="s">
@@ -9467,7 +9608,7 @@
       <c r="C138" t="s">
         <v>12</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="6">
         <v>4</v>
       </c>
       <c r="E138" s="2" t="s">
@@ -9496,7 +9637,7 @@
       <c r="C139" t="s">
         <v>12</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="6">
         <v>2</v>
       </c>
       <c r="E139" s="2" t="s">
@@ -9513,6 +9654,209 @@
       </c>
       <c r="I139" s="2" t="s">
         <v>657</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="6">
+        <v>2</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H140" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C141" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="6">
+        <v>2</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H141" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="6">
+        <v>2</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H142" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C143" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H143" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" s="6">
+        <v>1</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C146" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
